--- a/patent_analysis/stage.xlsx
+++ b/patent_analysis/stage.xlsx
@@ -11,6 +11,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成熟期" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初创期" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="种子期" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="种子期patent_count" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初创期patent_count" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="扩张期patent_count" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成熟期patent_count" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="种子期citation_count" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初创期citation_count" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="扩张期citation_count" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成熟期citation_count" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="种子期invention_count" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初创期invention_count" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="扩张期invention_count" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成熟期invention_count" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="种子期invention_citation" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初创期invention_citation" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="扩张期invention_citation" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成熟期invention_citation" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1237,6 +1253,2016 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.3249706567644369</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.04757709699287006</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-6.830401123741057</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>1.022337769995829e-11</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.4182579429079636</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>-0.2316833706209102</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.6170481153238677</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.09411280753492175</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>6.556473358792364</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>6.469624835858667e-11</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.4325154523159375</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.801580778331798</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.0483037881013287</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.1215775556784025</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0.3973084327266959</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.691168483906706</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.1900806645461574</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.2866882407488148</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-0.0005813314679878535</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.004104485210622336</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-0.1416332227202032</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.8873792972289172</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.008629243394446514</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.007466580458470806</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.002833613790716534</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.003867717251635259</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0.7326320944268847</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.463840470380902</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-0.004750052905669422</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.01041728048710249</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>-0.02827051675963401</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.1122152950105377</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>-0.2519310469840964</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.8011117341415606</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-0.2482978197473947</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.1917567862281266</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.1337006077368632</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.07084176626590653</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-1.887313300956025</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0.0591706837576611</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.2725784083623493</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.005177192888622784</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.21662094609648</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.08241360423235802</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>2.628461018228689</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.008601005139842854</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.05505777932776296</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.378184112865197</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>-0.0845716326774166</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.1393858363877903</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>-0.6067448090071853</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.5440452648579077</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.3578228433152326</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.1886795779603994</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-0.007364242332516813</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.004270475825868086</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-1.724454752303823</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.0846818341284461</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.01573605915163373</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.001007574486600105</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.0141197449452731</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.005466924144091791</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>2.582758526205741</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.009826924308227181</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0.003402417564303682</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.02483707232624251</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.246960143890718</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.1317194245985228</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>1.874895404709258</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.06085993981302984</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-0.0112618761424142</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.5051821639238501</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.105708036566321</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.05908087575324003</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-1.789209032848907</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0.07360178870496514</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.2215139838125667</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.01009791067992465</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.02325515117473342</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.06364104868788448</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0.3654111874991867</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.7148097617624076</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>-0.1014893085693442</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.147999610918811</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.009339636546050018</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.07806980009176885</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0.1196318747463365</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.9047764074824742</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.1436869906947711</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.1623662637868711</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-0.00769173434954492</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.00300688714526098</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-2.558038921303554</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.01053639140008289</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.01358561133901069</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>-0.001797857360079156</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.004292524769488198</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.003154012792997514</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>1.360972529667092</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.1735432852202254</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-0.001889736993952628</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.01047478653292902</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.2058893926819696</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.07655285929688867</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>2.689506238865431</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.007163876911298495</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0.05583616018907483</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.3559426251748644</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.08467292812846124</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.08159770626285399</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-1.03768760185122</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0.2994422647290813</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.2446221307043647</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.07527627444744224</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.06125653167887717</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.06718551189246731</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0.9117521018061204</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.3619226582575703</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>-0.07044164396881364</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.192954707326568</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.1712973951913981</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.1210299337873661</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1.415330818013545</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.1570047184673342</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.06594752606585921</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.4085423164486555</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-0.01205058137373017</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.004534069600346898</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-2.657784823772487</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.007878943573496056</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.02093834121667169</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>-0.003162821530788647</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.004941579035902038</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.004721286166600735</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>1.046659503687723</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.2952836140952479</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-0.004313165883615491</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.01419632395541957</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.1975828452297269</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.1247638644149671</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>1.583654419139843</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.1133060914747386</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-0.04698138993611772</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.4421470803955714</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.1758942508711706</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.03404260226756989</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-5.166886170706557</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>2.537151617687528e-07</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.2426436361747965</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>-0.1091448655675447</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.2571056641180137</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.0728978285636611</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>3.526931723260938</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.000426749333301224</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.1141704910560858</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.4000408371799415</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.01774229897138254</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.09341706794579249</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0.189925667348904</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.84938031446924</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.1654261854246789</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.200910783367444</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>0.0005019852242195841</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.003220991442869785</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0.1558480465171102</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.8761633535409763</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.0058136071382542</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.006817577586693368</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.001677822027522153</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.002429783848048404</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0.6905231627372022</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.4899190265939297</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-0.003086401841239312</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.006442045896283619</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>-0.004859118937144296</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.09533563965573728</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>-0.05096854602004944</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.9593540005394219</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-0.1917894627026271</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.1820712248283385</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.02581082802095317</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.0445941047135831</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-0.578794622893087</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0.5627514048542914</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.1132328603886803</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.06161120434677397</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.01803596317874977</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.06574876848587463</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0.274316365068109</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.7838517870552639</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>-0.1108575532092932</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.1469294795667928</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.0237384921247636</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.1067271712780891</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0.222422198962909</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.823993471577126</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.1854888548959987</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.2329658391455258</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-0.004215636088666527</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.003043861151275282</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-1.384963334119333</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.1661197193552675</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.01018280439036812</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.00175153221303507</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.00955647482048458</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.003926466596948427</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>2.433861229817079</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.0149702695199585</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0.001859051761228276</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.01725389787974088</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.1152242271099774</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.1002737646563531</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>1.14909645114912</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.2505660619705856</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-0.08135189782232646</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.3118003520422813</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.03962434786016335</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.03620590594057298</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-1.094416693375972</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0.2737902417973308</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.1105924772235232</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.03134378150319647</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>-0.1025850260160117</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.04555707057196119</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>-2.251791538131717</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.02435018411261725</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>-0.1918826141794827</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>-0.01328743785254068</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.02168509161358</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.05804955599027413</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0.3735617136712158</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.7087358232769785</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.09209933918523064</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.1354695224123906</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-0.006016863995913016</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.002159484589617433</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-2.786250026900606</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.00533902256066443</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.01024972539608619</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>-0.001784002595739842</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.004694691266812263</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.001933497687323424</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>2.428082173354553</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.01519085219064475</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0.0009047926181512352</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.008484589915473292</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.1663242697974009</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.05616363649800239</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>2.961422731295484</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.00306712022291511</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0.05623647840090504</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.2764120611938968</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.00662878349587567</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.05758927567095049</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-0.1151044776765511</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0.9083647743463388</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.1195162547541913</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.1062586877624399</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>-0.07481487735222689</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.048204816391718</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>-1.552020792782871</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.1206909819539088</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>-0.1693067729618359</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.01967701825738208</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.1588337705568382</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.100715519766493</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1.577053575507441</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.1148169165420341</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.03859049308329951</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.3562580341969759</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-0.01064563594485898</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.003456797803048698</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-3.07962355665412</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.002078615677717277</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.01742170940803522</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>-0.003869562481682745</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.003400337763689547</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.003462606645156231</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0.9820167614032075</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.3261169158612063</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-0.003387122289938093</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.01018779781731719</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.1182439215962324</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.1042910776246482</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>1.133787513652908</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.2569126625816158</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-0.08618921097379439</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.3226770541662591</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.2654940607231799</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.04345745184673067</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-6.109287347531243</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>1.130684212924393e-09</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.3507037099395253</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>-0.1802844115068346</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.5094043202098506</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.09170399271480378</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>5.5548761305746</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>3.022778671812887e-08</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.3295947658317888</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.6892138745879124</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.06340667813072301</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.1190344548600284</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0.5326749990604179</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.5942982915789101</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.169991363223719</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.2968047194851651</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-0.001516952513230516</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.003972675266540308</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-0.3818465923975678</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.7026023827705443</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.009306416725403768</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.006272511698942735</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.002341196358345137</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.003688942883009206</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0.6346523740251944</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.5257038810429429</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-0.004891936641467313</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.009574329358157588</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>-0.04079907059579103</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.1086085881804163</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>-0.3756523427780613</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.7072021092670902</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-0.2537544857769506</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.1721563445853686</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.1398370192284976</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.06467230987925358</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-2.162239442036016</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0.03064260262317053</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.2666202522112572</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>-0.013053786245738</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.1639738303781015</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.07467307025029285</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>2.195889760906924</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.02814134768151977</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.0175851629444384</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.3103624978117646</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>-0.02359301405313951</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.1299125834918521</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>-0.1816068422241732</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.8558979552672361</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.2782729129309031</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.231086884824624</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-0.007891155150744119</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.00406763188951204</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-1.939987532079938</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.05243213866996288</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.01586531785652901</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>8.300755504077328e-05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.01122315585241096</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.005100599040133889</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>2.200360342795414</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.02782266894406416</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0.001223970147365002</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.02122234155745692</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.1788073398659304</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.122293719611722</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>1.462113838990563</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.1437670158519309</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-0.06093658106111627</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.4185512607929771</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1431,6 +3457,408 @@
       </c>
       <c r="G7" s="0" t="n">
         <v>0.3574944955409732</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.1037333682559035</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.05471690170820191</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-1.895819482051451</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0.05800356054382472</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.2109853775044384</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.003518640992631383</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>-0.006993320667040308</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.06035790528471576</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>-0.1158642042670623</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.9077617519690993</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>-0.1253024064106172</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.1113157650765366</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.02102569206662102</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.07156750916036085</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0.2937882331423452</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.7689238849731765</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.1192556271370036</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.1613070112702457</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-0.008348857212129119</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.002802527106281841</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-2.979046016509609</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.002896208255025456</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.01384216282225204</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>-0.002855551602006204</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.005227376465638508</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.002809779843228611</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>1.860422081906577</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.06284583659851095</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-0.0002801454210974432</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.01073489835237446</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.1777228093067672</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.06914811986889052</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>2.570175583135761</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.01017447927384385</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0.04218379740790149</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.313261821205633</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.04229525385003687</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.07698903035874351</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.5493672754800902</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5827665036740681</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.193210452045736</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1086199443456622</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.02183918426635508</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.06408905384605974</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3407630937852857</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7332895670382187</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.1037892619978016</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1474676305305118</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2038303731277728</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1139511025347624</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.788752970297864</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07368686355455134</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.0195385034968576</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4271992497524032</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.01554367411491727</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.004273608491326259</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-3.637131044283723</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0002771699147834372</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.02392087369093555</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.00716647453889898</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.00564299754650873</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.00433577359794806</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.301497280480541</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1931202556121281</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.002856059121915712</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01414205421493317</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1600021031826819</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1168494269326405</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.369301565123785</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1709378087612761</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.06904811789976345</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3890523242651273</v>
       </c>
     </row>
   </sheetData>
@@ -1485,152 +3913,152 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>treatment</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="0" t="n">
         <v>-0.04387152544408174</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="0" t="n">
         <v>0.07161227580102528</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="0" t="n">
         <v>-0.6126257677661129</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="0" t="n">
         <v>0.540138665983688</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="0" t="n">
         <v>-0.1842471185045212</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="0" t="n">
         <v>0.09650406761635769</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>treatment_post</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="0" t="n">
         <v>-0.05048590950847504</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="0" t="n">
         <v>0.05917338439115283</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="0" t="n">
         <v>-0.8531861077059388</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="0" t="n">
         <v>0.3935778893546904</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="0" t="n">
         <v>-0.1664785774468748</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="0" t="n">
         <v>0.06550675842992475</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>lnGDP</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="0" t="n">
         <v>0.1431926341069207</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="0" t="n">
         <v>0.1164957068984644</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="0" t="n">
         <v>1.229166618403585</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="0" t="n">
         <v>0.2190401718911952</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="0" t="n">
         <v>-0.08516421898771223</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="0" t="n">
         <v>0.3715494872015536</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>二产就业比例</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="0" t="n">
         <v>-0.007318277993199441</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="0" t="n">
         <v>0.004239105732463603</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="0" t="n">
         <v>-1.726373073725232</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="0" t="n">
         <v>0.08431324054100164</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="0" t="n">
         <v>-0.01562784467830076</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="0" t="n">
         <v>0.0009912886919018742</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>城镇化率</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="0" t="n">
         <v>0.003323418252746215</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="0" t="n">
         <v>0.004172406912973951</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="0" t="n">
         <v>0.7965230434290013</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="0" t="n">
         <v>0.4257482441359053</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="0" t="n">
         <v>-0.004855404279379067</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="0" t="n">
         <v>0.0115022407848715</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>lnFixedInvestment</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="0" t="n">
         <v>0.2090708066703096</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>0.1208243927443626</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="0" t="n">
         <v>1.730369190538013</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="0" t="n">
         <v>0.08359722141636028</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="0" t="n">
         <v>-0.02777120956141757</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="0" t="n">
         <v>0.4459128229020367</v>
       </c>
     </row>
@@ -2039,4 +4467,808 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.2931276466457742</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.04688175885937786</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-6.252488255080455</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>4.616822479874827e-10</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.3850515413357342</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>-0.2012037519558141</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.4596893123078689</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.08118449565271577</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>5.662279584445401</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>1.635906610175653e-08</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.3005059708461618</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.6188726537695761</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>-0.02918967315634904</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.1099555335582793</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>-0.2654679779338051</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.7906673374492055</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.2447861254504548</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.1864067791377567</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>0.00323131798972435</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.003913958862555658</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0.8255881329356713</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.4091038553643336</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.004443017424644029</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.01090565340409273</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.002080785147376131</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.003060287622102749</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0.6799312366418705</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.4966008162148525</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-0.003919705532569625</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.008081275827321887</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.02288549615165637</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.1117759106753063</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0.2047444392391093</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.8377857809503373</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-0.196280279445859</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.2420512717491717</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.07056834965670646</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.06000934095554643</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-1.17595608505319</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0.2396632031639192</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.1882103245562229</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.04707362524281004</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.1658632939566787</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.08093256135264607</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>2.04940126921185</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.04047011532481704</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.007203555329411387</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.3245230325839461</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>-0.04885318716709928</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.1327029858320863</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>-0.3681393215139478</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.712783486102285</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.3090033751172351</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.2112970007830366</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-0.003022147077644503</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.003794884427323545</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-0.7963739437977989</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.425849009633593</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.01046161719074695</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.004417323035457946</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.01357461058059578</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.00488719020335113</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>2.777589988473891</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.005494880553256642</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0.003993790360328767</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.02315543080086279</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.209672171818151</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.1255491782909075</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>1.670040176068089</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.0949681839635601</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-0.03645373201563765</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.4557980756519397</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.09703031571514564</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.04717939924425443</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-2.056624655451968</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0.03973999733654798</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.1895078721212059</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>-0.004552759309085413</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>-0.04961448496610415</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.05435434057682092</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>-0.9127971094779861</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.3613642652821079</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>-0.1561558287967869</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.05692685886457859</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.02547562792811608</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.07467016576694144</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0.3411754569774218</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.7329763866879371</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.1208872884543585</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.1718385443105906</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-0.005393590803063042</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.002810623458133889</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-1.919001560829536</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.0550035244718825</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.01090276628111719</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.0001155846749911031</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.002582053129202629</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.002691999731456579</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0.9591580188626317</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.3374949595685381</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-0.002694604924920265</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.007858711183325522</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.2152360976585602</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.07257615804717059</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>2.96565846760128</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.003025222204047662</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0.07297769977614729</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.3574944955409732</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间下限</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>置信区间上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-0.04387152544408174</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0.07161227580102528</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>-0.6126257677661129</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0.540138665983688</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-0.1842471185045212</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.09650406761635769</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>treatment_post</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>-0.05048590950847504</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.05917338439115283</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>-0.8531861077059388</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.3935778893546904</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>-0.1664785774468748</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.06550675842992475</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>lnGDP</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.1431926341069207</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.1164957068984644</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1.229166618403585</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.2190401718911952</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-0.08516421898771223</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.3715494872015536</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>二产就业比例</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>-0.007318277993199441</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.004239105732463603</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>-1.726373073725232</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.08431324054100164</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-0.01562784467830076</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.0009912886919018742</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>城镇化率</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.003323418252746215</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.004172406912973951</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0.7965230434290013</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.4257482441359053</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-0.004855404279379067</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.0115022407848715</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>lnFixedInvestment</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.2090708066703096</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.1208243927443626</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>1.730369190538013</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.08359722141636028</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-0.02777120956141757</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.4459128229020367</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>